--- a/Data/Commodore 64/250407/Data C64 250407.xlsx
+++ b/Data/Commodore 64/250407/Data C64 250407.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Development\Visual Studio\Commodore-Repair-Toolbox\Data\Commodore 64\250407\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D02D0509-1FC3-45E0-A329-3C428A75ABB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960FE043-71D0-4930-B052-F675AD592311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10557" uniqueCount="2111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10558" uniqueCount="2112">
   <si>
     <t>Name</t>
   </si>
@@ -6463,6 +6463,12 @@
     <t>Oscilloscope baseline</t>
   </si>
   <si>
+    <t>Board layout (CBM)</t>
+  </si>
+  <si>
+    <t>Component pinouts</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve"># Revision date: </t>
     </r>
@@ -6475,14 +6481,11 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-March-4</t>
+      <t>2026-March-7</t>
     </r>
   </si>
   <si>
-    <t>Board layout (CBM)</t>
-  </si>
-  <si>
-    <t>Component pinouts</t>
+    <t>2026-March-7</t>
   </si>
 </sst>
 </file>
@@ -7115,7 +7118,7 @@
     </row>
     <row r="3" spans="1:7" s="13" customFormat="1" ht="21">
       <c r="A3" s="13" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -7206,7 +7209,7 @@
     </row>
     <row r="11" spans="1:7" s="6" customFormat="1">
       <c r="A11" s="6" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>752</v>
@@ -7397,7 +7400,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D457A7-C8EF-467F-8532-E177504F5ACE}">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="83.5546875" customWidth="1"/>
@@ -7446,6 +7449,11 @@
     <row r="11" spans="1:1">
       <c r="A11" t="s">
         <v>2102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>2111</v>
       </c>
     </row>
   </sheetData>
@@ -62563,7 +62571,7 @@
         <v>495</v>
       </c>
       <c r="B10" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="C10" t="s">
         <v>2104</v>
@@ -62634,7 +62642,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="C16" t="s">
         <v>445</v>
